--- a/tools/json_message_calculator.xlsx
+++ b/tools/json_message_calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\ESPIDF_Projects\ESP32P4_Time_Server\misc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\ESP32TimeServer\tools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B865AD0-E8CA-436D-9079-EDE17E8EBD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70433803-C8D9-4608-AED8-508424E4D666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10725" yWindow="4260" windowWidth="16410" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JSON Size Calculator" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="171">
   <si>
     <t>Component / JSON key or structural token</t>
   </si>
@@ -359,9 +359,6 @@
     <t>Future 19</t>
   </si>
   <si>
-    <t>Future 20</t>
-  </si>
-  <si>
     <t>Grand total</t>
   </si>
   <si>
@@ -543,6 +540,12 @@
   </si>
   <si>
     <t>https://github.com/roblatour/ESP32TimeServer/tree/main/misc</t>
+  </si>
+  <si>
+    <t>"load_shedding":,</t>
+  </si>
+  <si>
+    <t>load_shedding</t>
   </si>
 </sst>
 </file>
@@ -972,21 +975,21 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" s="7">
         <v>500</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1012,10 +1015,10 @@
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1052,7 +1055,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1076,7 +1079,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="J6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1084,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7">
         <v>24</v>
@@ -1096,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <f t="shared" ref="F7:F70" si="2">LEN(B7)</f>
+        <f t="shared" ref="F7:F71" si="2">LEN(B7)</f>
         <v>10</v>
       </c>
       <c r="G7">
@@ -1113,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1142,7 +1145,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1171,7 +1174,7 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1229,7 +1232,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1258,7 +1261,7 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1287,7 +1290,7 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1316,7 +1319,7 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1345,7 +1348,7 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1403,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1461,7 +1464,7 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -1485,7 +1488,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1493,7 +1496,7 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21">
         <v>10</v>
@@ -1517,7 +1520,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1525,7 +1528,7 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -1549,7 +1552,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1586,7 +1589,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -1610,7 +1613,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1638,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="3" t="str">
-        <f t="shared" ref="I25:I88" si="3">IF(C25-D25&gt;0," * ", " ")</f>
+        <f t="shared" ref="I25:I89" si="3">IF(C25-D25&gt;0," * ", " ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -1676,7 +1679,7 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -1700,7 +1703,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,7 +1711,7 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -1732,7 +1735,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1740,7 +1743,7 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -1764,7 +1767,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1772,7 +1775,7 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -1796,7 +1799,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1862,7 +1865,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -1886,7 +1889,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1894,7 +1897,7 @@
         <v>44</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -1918,7 +1921,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1984,7 +1987,7 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C37">
         <v>19</v>
@@ -2000,7 +2003,7 @@
         <v>20</v>
       </c>
       <c r="G37">
-        <f t="shared" ref="G37:G68" si="4">(D37+F37)*E37</f>
+        <f t="shared" ref="G37:G69" si="4">(D37+F37)*E37</f>
         <v>27</v>
       </c>
       <c r="I37" s="3" t="str">
@@ -2008,7 +2011,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2016,7 +2019,7 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -2040,7 +2043,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2048,7 +2051,7 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39">
         <v>10</v>
@@ -2072,7 +2075,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2109,7 +2112,7 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41">
         <v>10</v>
@@ -2133,7 +2136,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2141,7 +2144,7 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -2165,7 +2168,7 @@
         <v xml:space="preserve"> * </v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -2260,7 +2263,7 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -2284,7 +2287,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -2292,7 +2295,7 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2316,242 +2319,243 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C48">
-        <v>10</v>
-      </c>
-      <c r="D48">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>5</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G48">
-        <f t="shared" si="4"/>
-        <v>31</v>
+        <f>(D48+F48)*E48</f>
+        <v>22</v>
       </c>
       <c r="I48" s="3" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>122</v>
-      </c>
+      <c r="J48" s="4"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49">
+        <v>10</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="G49">
+        <f>(D49+F49)*E49</f>
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>62</v>
       </c>
-      <c r="B49" t="s">
-        <v>160</v>
-      </c>
-      <c r="C49">
-        <v>10</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+      <c r="D50" s="5">
         <v>5</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49">
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="G49">
+      <c r="G50">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="I49" s="3" t="str">
+      <c r="I50" s="3" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * </v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="J50" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>63</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>22</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G50">
+      <c r="G51">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I50" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="I51" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>64</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>65</v>
       </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="G51">
+      <c r="G52">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="I51" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="I52" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>66</v>
       </c>
-      <c r="B52" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="D52">
-        <v>10</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52">
+      <c r="B53" t="s">
+        <v>160</v>
+      </c>
+      <c r="C53">
+        <v>10</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G52">
+      <c r="G53">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="I52" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="I53" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>67</v>
       </c>
-      <c r="B53" t="s">
-        <v>162</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-      <c r="D53">
-        <v>10</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
+      <c r="B54" t="s">
+        <v>161</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="G53">
+      <c r="G54">
         <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="I53" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="I54" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>68</v>
       </c>
-      <c r="B54" t="s">
-        <v>163</v>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-      <c r="D54">
-        <v>10</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54">
+      <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55">
+        <v>10</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="G54">
+      <c r="G55">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="I54" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="I55" s="3" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
@@ -2559,10 +2563,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2575,11 +2579,11 @@
       </c>
       <c r="F56">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" s="3" t="str">
         <f t="shared" si="3"/>
@@ -2588,10 +2592,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2604,11 +2608,11 @@
       </c>
       <c r="F57">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G57">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I57" s="3" t="str">
         <f t="shared" si="3"/>
@@ -2617,323 +2621,323 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="I58" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>74</v>
       </c>
-      <c r="B58" t="s">
-        <v>164</v>
-      </c>
-      <c r="C58">
+      <c r="B59" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59">
         <v>49</v>
       </c>
-      <c r="D58">
+      <c r="D59">
         <v>49</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E59" s="7">
         <f>B2</f>
         <v>500</v>
       </c>
-      <c r="F58">
+      <c r="F59">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="G58">
-        <f>(D58+F58)*E58</f>
+      <c r="G59">
+        <f>(D59+F59)*E59</f>
         <v>37500</v>
       </c>
-      <c r="I58" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J58" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="I59" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J59" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>75</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>32</v>
       </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <f>E58-1</f>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <f>E59-1</f>
         <v>499</v>
       </c>
-      <c r="F59">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G59">
+      <c r="F60">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G60">
         <f t="shared" si="4"/>
         <v>499</v>
       </c>
-      <c r="I59" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="I60" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>76</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>77</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I60" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="I61" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>78</v>
       </c>
-      <c r="B61" t="s">
-        <v>145</v>
-      </c>
-      <c r="C61">
+      <c r="B62" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62">
         <v>5</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <v>5</v>
       </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61">
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="G61">
+      <c r="G62">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="I61" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="I62" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>79</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>22</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62">
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G62">
+      <c r="G63">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I62" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="I63" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>80</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
         <v>81</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="G63">
+      <c r="G64">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="I63" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="I64" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>82</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>83</v>
       </c>
-      <c r="C64">
-        <v>0</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64">
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="G64">
+      <c r="G65">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="I64" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="I65" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>66</v>
       </c>
-      <c r="B65" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65">
+      <c r="B66" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66">
         <v>24</v>
       </c>
-      <c r="D65">
+      <c r="D66">
         <v>24</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65">
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="G65">
+      <c r="G66">
         <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="I65" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="I66" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>67</v>
       </c>
-      <c r="B66" t="s">
-        <v>147</v>
-      </c>
-      <c r="C66">
+      <c r="B67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67">
         <v>24</v>
       </c>
-      <c r="D66">
+      <c r="D67">
         <v>24</v>
       </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66">
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="G66">
+      <c r="G67">
         <f t="shared" si="4"/>
         <v>49</v>
       </c>
-      <c r="I66" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="I67" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>68</v>
       </c>
-      <c r="B67" t="s">
-        <v>148</v>
-      </c>
-      <c r="C67">
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68">
         <v>24</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <v>24</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="G67">
+      <c r="G68">
         <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="I67" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>84</v>
-      </c>
-      <c r="B68" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="I68" s="3" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
@@ -2941,7 +2945,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B69" t="s">
         <v>70</v>
@@ -2960,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <f t="shared" ref="G69:G91" si="5">(D69+F69)*E69</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I69" s="3" t="str">
@@ -2970,7 +2974,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B70" t="s">
         <v>70</v>
@@ -2989,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G70:G91" si="5">(D70+F70)*E70</f>
         <v>1</v>
       </c>
       <c r="I70" s="3" t="str">
@@ -2999,10 +3003,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3014,6 +3018,7 @@
         <v>1</v>
       </c>
       <c r="F71">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G71">
@@ -3027,7 +3032,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="B72" t="s">
+        <v>88</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3036,14 +3044,14 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="3" t="str">
         <f t="shared" si="3"/>
@@ -3052,7 +3060,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3077,7 +3085,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3102,7 +3110,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3127,7 +3135,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3152,7 +3160,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3177,7 +3185,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3202,7 +3210,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3227,7 +3235,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3252,7 +3260,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3277,7 +3285,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3302,7 +3310,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3327,7 +3335,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3352,7 +3360,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3377,7 +3385,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3402,7 +3410,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3427,7 +3435,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3452,7 +3460,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3471,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="str">
-        <f t="shared" ref="I89:I91" si="6">IF(C89-D89&gt;0," * ", " ")</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3496,13 +3504,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I90:I91" si="6">IF(C90-D90&gt;0," * ", " ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3528,23 +3536,23 @@
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C92" s="9">
         <f>SUM(C5:C91)</f>
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D92" s="9">
         <f>SUM(D5:D91)</f>
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F92" s="9">
         <f>SUM(F5:F91)</f>
-        <v>883</v>
+        <v>900</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="6"/>
@@ -3552,7 +3560,7 @@
       <c r="F94" s="6"/>
       <c r="G94" s="6">
         <f>SUM(G5:G91)</f>
-        <v>39144</v>
+        <v>39166</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -3566,15 +3574,15 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B96" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
